--- a/docs/table-definition.xlsx
+++ b/docs/table-definition.xlsx
@@ -279,9 +279,21 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">関連ドキュメント</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">基本設計書 (./basic-design.md) / 実装手順書 (./implementation-guide.md)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">DDL は MySQL 公式イメージの /docker-entrypoint-initdb.d にマウントされ、DB ボリュームが空の初回起動時のみ自動実行される。再投入は make seed (volume 削除 → 再 up)。</t>
         </is>

--- a/docs/table-definition.xlsx
+++ b/docs/table-definition.xlsx
@@ -287,7 +287,7 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">基本設計書 (./basic-design.md) / 実装手順書 (./implementation-guide.md)</t>
+          <t xml:space="preserve">基本設計書 (./basic-design.md) / API 仕様書 (./api-spec.md) / 実装手順書 (./implementation-guide.md)</t>
         </is>
       </c>
     </row>
